--- a/Version01/sesion1/Encuesta.xlsx
+++ b/Version01/sesion1/Encuesta.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ljcr/Documents/GitHub/Datajupyer/Version01/sesion1/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AE3114-98D7-4A4D-A973-016033AA1B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId3"/>
+    <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -238,24 +247,27 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -264,43 +276,364 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="21.57"/>
-    <col customWidth="1" min="5" max="5" width="65.71"/>
-    <col customWidth="1" min="6" max="8" width="21.57"/>
+    <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="80.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="115" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="116" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="87.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="76" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -326,7 +659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
         <v>42591.427718125</v>
       </c>
@@ -352,9 +685,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1">
-        <v>42591.42815969908</v>
+        <v>42591.428159699077</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
@@ -378,9 +711,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1">
-        <v>42591.43277121527</v>
+        <v>42591.432771215274</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>8</v>
@@ -404,9 +737,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
-        <v>42591.43487927083</v>
+        <v>42591.434879270833</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
@@ -430,7 +763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>42591.43558153935</v>
       </c>
@@ -456,7 +789,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>42591.43595694445</v>
       </c>
@@ -482,7 +815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>42591.436483784724</v>
       </c>
@@ -508,9 +841,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
-        <v>42591.43686702546</v>
+        <v>42591.436867025463</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>8</v>
@@ -534,9 +867,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
-        <v>42591.43716412037</v>
+        <v>42591.437164120369</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
@@ -560,7 +893,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>42591.43766221065</v>
       </c>
@@ -586,7 +919,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>42591.43800465278</v>
       </c>
@@ -612,7 +945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>42591.43838673611</v>
       </c>
@@ -638,9 +971,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
-        <v>42591.43878386574</v>
+        <v>42591.438783865742</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
@@ -664,9 +997,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
-        <v>42591.43918570602</v>
+        <v>42591.439185706018</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>8</v>
@@ -690,9 +1023,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
-        <v>42591.4397553125</v>
+        <v>42591.439755312502</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>8</v>
@@ -716,9 +1049,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
-        <v>42591.44014133102</v>
+        <v>42591.440141331019</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -742,9 +1075,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
-        <v>42591.4405987963</v>
+        <v>42591.440598796296</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
@@ -768,9 +1101,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
-        <v>42591.44090252314</v>
+        <v>42591.440902523143</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>8</v>
@@ -794,7 +1127,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>42591.441203298615</v>
       </c>
@@ -820,9 +1153,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
-        <v>42591.4417985301</v>
+        <v>42591.441798530097</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>8</v>
@@ -846,7 +1179,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>42591.44351582176</v>
       </c>
@@ -872,7 +1205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>42591.44395158565</v>
       </c>
@@ -898,7 +1231,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>42591.4443316088</v>
       </c>
@@ -924,9 +1257,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
-        <v>42591.44465976852</v>
+        <v>42591.444659768516</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>46</v>
@@ -950,9 +1283,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
-        <v>42591.44496840278</v>
+        <v>42591.444968402779</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>46</v>
@@ -976,7 +1309,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>42591.44535008102</v>
       </c>
@@ -1002,9 +1335,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
-        <v>42591.44572800926</v>
+        <v>42591.445728009261</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>46</v>
@@ -1028,9 +1361,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
-        <v>42591.44617243056</v>
+        <v>42591.446172430558</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>46</v>
@@ -1054,7 +1387,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>42591.446538425924</v>
       </c>
@@ -1080,9 +1413,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
-        <v>42591.44695403935</v>
+        <v>42591.446954039347</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>46</v>
@@ -1106,9 +1439,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
-        <v>42591.44744134259</v>
+        <v>42591.447441342592</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>46</v>
@@ -1132,7 +1465,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>42591.447924884254</v>
       </c>
@@ -1158,7 +1491,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>42591.448186423615</v>
       </c>
@@ -1184,9 +1517,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
-        <v>42591.44877466436</v>
+        <v>42591.448774664357</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>46</v>
@@ -1210,9 +1543,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
-        <v>42591.44923611111</v>
+        <v>42591.449236111112</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>46</v>
@@ -1236,9 +1569,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
-        <v>42591.44957943287</v>
+        <v>42591.449579432869</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>46</v>
@@ -1262,9 +1595,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
-        <v>42591.45007641204</v>
+        <v>42591.450076412038</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>46</v>
@@ -1288,7 +1621,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>42591.45044601852</v>
       </c>
@@ -1314,7 +1647,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>42594.531646145835</v>
       </c>
@@ -1340,9 +1673,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>42594.53219994213</v>
+        <v>42594.532199942128</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>67</v>
@@ -1366,9 +1699,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>42594.532719375</v>
+        <v>42594.532719374998</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>67</v>
@@ -1392,7 +1725,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>42594.533027708334</v>
       </c>
@@ -1418,9 +1751,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>42594.53348832176</v>
+        <v>42594.533488321758</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>67</v>
@@ -1445,6 +1778,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>